--- a/artfynd/A 22210-2025 artfynd.xlsx
+++ b/artfynd/A 22210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101554951</v>
+        <v>101555002</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>laxsjöåsen, Mpd</t>
+          <t>Laxsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613526.8853341658</v>
+        <v>613460</v>
       </c>
       <c r="R2" t="n">
-        <v>6967060.383203867</v>
+        <v>6966982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101554989</v>
+        <v>101690025</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,14 +814,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Laxsjöåsen, Mpd</t>
+          <t>laxsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613634.9689324361</v>
+        <v>613460</v>
       </c>
       <c r="R3" t="n">
-        <v>6966982.674063317</v>
+        <v>6967075</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101690025</v>
+        <v>123301100</v>
       </c>
       <c r="B4" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>laxsjöåsen, Mpd</t>
+          <t>NV Aldersjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613459.9213513136</v>
+        <v>613493</v>
       </c>
       <c r="R4" t="n">
-        <v>6967075.454870394</v>
+        <v>6966942</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,24 +948,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på tallåga med bark kvar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,38 +984,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Douglas Skarp, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123435060</v>
+        <v>101554951</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,16 +1035,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NV Aldersjön, Mpd</t>
+          <t>laxsjöåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613517</v>
+        <v>613527</v>
       </c>
       <c r="R5" t="n">
-        <v>6967074</v>
+        <v>6967060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,34 +1072,14 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:58</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på östra sidan av traktorbilväg i höjd med sälg</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,23 +1088,250 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123435060</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NV Aldersjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613517</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967074</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på östra sidan av traktorbilväg i höjd med sälg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Douglas Skarp, Simon Selberg, Linnéa Kjellberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnéa Kjellberg, Simon Selberg, Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101554989</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laxsjöåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>613635</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966982</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 22210-2025 artfynd.xlsx
+++ b/artfynd/A 22210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101555002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101690025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301100</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1128,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554951</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123435060</t>
         </is>
       </c>
     </row>
@@ -1334,8 +1364,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101554989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>